--- a/artfynd/A 36353-2023 artfynd.xlsx
+++ b/artfynd/A 36353-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121138310</v>
       </c>
       <c r="B2" t="n">
-        <v>97028</v>
+        <v>97038</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 36353-2023 artfynd.xlsx
+++ b/artfynd/A 36353-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121138310</v>
       </c>
       <c r="B2" t="n">
-        <v>97038</v>
+        <v>97051</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 36353-2023 artfynd.xlsx
+++ b/artfynd/A 36353-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121138310</v>
       </c>
       <c r="B2" t="n">
-        <v>97051</v>
+        <v>97052</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 36353-2023 artfynd.xlsx
+++ b/artfynd/A 36353-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121138310</v>
       </c>
       <c r="B2" t="n">
-        <v>97052</v>
+        <v>97055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 36353-2023 artfynd.xlsx
+++ b/artfynd/A 36353-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121138310</v>
       </c>
       <c r="B2" t="n">
-        <v>97055</v>
+        <v>97061</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 36353-2023 artfynd.xlsx
+++ b/artfynd/A 36353-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121138310</v>
       </c>
       <c r="B2" t="n">
-        <v>97061</v>
+        <v>97062</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
